--- a/data/trans_orig/P2C_R1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1769</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6330</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1769</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6920</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140627</t>
+          <t>140685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306071</t>
+          <t>306661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>283934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>285959</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341974</t>
+          <t>342055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353047</t>
+          <t>353056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>628269</t>
+          <t>628255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>638450</t>
+          <t>639020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -1419,97 +1419,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7313</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2135</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7152</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6536</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>7460</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188213</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>190164</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218857</t>
+          <t>218696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>408713</t>
+          <t>409637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,62 +1797,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1838</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5894</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5440</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193840</t>
+          <t>193223</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245241</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438910</t>
+          <t>438456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98137</t>
+          <t>98303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141143</t>
+          <t>142364</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244507</t>
+          <t>244121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255920</t>
+          <t>255692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7132</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2280</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7718</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8266</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2280</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>7955</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160441</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>170761</t>
+          <t>171347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>332888</t>
+          <t>332577</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>347315</t>
+          <t>346861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>437955</t>
+          <t>437964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788837</t>
+          <t>788911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>18257</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>454846</t>
+          <t>453296</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>465087</t>
+          <t>465078</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>526113</t>
+          <t>525847</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>537064</t>
+          <t>537073</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>985851</t>
+          <t>986557</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1000944</t>
+          <t>1000665</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1889549</t>
+          <t>1890151</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1905490</t>
+          <t>1904747</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2271632</t>
+          <t>2273189</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2290698</t>
+          <t>2291168</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4166825</t>
+          <t>4170160</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4192098</t>
+          <t>4192924</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24299</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167183</t>
+          <t>168757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176758</t>
+          <t>176771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189413</t>
+          <t>189065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>204677</t>
+          <t>203990</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>362109</t>
+          <t>361711</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>378954</t>
+          <t>379521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311966</t>
+          <t>312474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350853</t>
+          <t>350901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>666621</t>
+          <t>666121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674288</t>
+          <t>674281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4742,97 +4742,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8337</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2521</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>8396</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>8800</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>203217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230708</t>
+          <t>231262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>435994</t>
+          <t>436398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241668</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>243766</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281806</t>
+          <t>282047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290850</t>
+          <t>290821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525226</t>
+          <t>525482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>534535</t>
+          <t>534558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,62 +5463,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>10973</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>10999</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134198</t>
+          <t>131174</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166541</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300604</t>
+          <t>300630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,62 +5806,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6769</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5902</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170078</t>
+          <t>169465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>202376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204356</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>374412</t>
+          <t>373545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20712</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>384049</t>
+          <t>384067</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>395839</t>
+          <t>395923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>444155</t>
+          <t>442993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>454424</t>
+          <t>453600</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>832837</t>
+          <t>832471</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>848265</t>
+          <t>848147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>469778</t>
+          <t>469319</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>582181</t>
+          <t>582216</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1056372</t>
+          <t>1055456</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1064775</t>
+          <t>1064774</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32174</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61541</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2110561</t>
+          <t>2108907</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2127869</t>
+          <t>2127599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2475073</t>
+          <t>2475246</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2497833</t>
+          <t>2498774</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4592615</t>
+          <t>4592781</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4621982</t>
+          <t>4622464</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168114</t>
+          <t>167757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192118</t>
+          <t>191573</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199314</t>
+          <t>199318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>363771</t>
+          <t>364651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372684</t>
+          <t>372761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253864</t>
+          <t>254862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314641</t>
+          <t>314948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>573790</t>
+          <t>574138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>583458</t>
+          <t>583521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172074</t>
+          <t>172662</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206370</t>
+          <t>206173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>382086</t>
+          <t>381979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>389805</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189562</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191516</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247398</t>
+          <t>247248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438957</t>
+          <t>439554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>446290</t>
+          <t>446302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11179</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122998</t>
+          <t>122648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132802</t>
+          <t>132776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143632</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145518</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268141</t>
+          <t>268284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278311</t>
+          <t>278312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>809</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153031</t>
+          <t>153179</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160418</t>
+          <t>160412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164741</t>
+          <t>165736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>322298</t>
+          <t>323102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>331686</t>
+          <t>331857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>332759</t>
+          <t>332562</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>435125</t>
+          <t>435091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>442536</t>
+          <t>442544</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>771363</t>
+          <t>772347</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>781717</t>
+          <t>781788</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>446508</t>
+          <t>446724</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>455843</t>
+          <t>455695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>567086</t>
+          <t>567828</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>580094</t>
+          <t>580667</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1018673</t>
+          <t>1020837</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1034370</t>
+          <t>1035092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54728</t>
+          <t>54523</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1869819</t>
+          <t>1869753</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1886325</t>
+          <t>1886093</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2299130</t>
+          <t>2301530</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2320607</t>
+          <t>2320099</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4177220</t>
+          <t>4177425</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4202535</t>
+          <t>4203913</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13755</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30200</t>
+          <t>29851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>42323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>25914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>45066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44757</t>
+          <t>43649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59999</t>
+          <t>59825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88418</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100390</t>
+          <t>100905</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137776</t>
+          <t>137107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157191</t>
+          <t>156259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25753</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>26144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>35024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34277</t>
+          <t>33927</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45869</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61760</t>
+          <t>61362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>77289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,72%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19522</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39892</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>51353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56772</t>
+          <t>56258</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66115</t>
+          <t>66186</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96444</t>
+          <t>95296</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115128</t>
+          <t>114877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20821</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20739</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38004</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45988</t>
+          <t>45658</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23521</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23983</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38852</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48692</t>
+          <t>48707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47279</t>
+          <t>47536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57315</t>
+          <t>57090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89186</t>
+          <t>88823</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103788</t>
+          <t>102998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57714</t>
+          <t>58498</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54254</t>
+          <t>55304</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38074</t>
+          <t>38983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46237</t>
+          <t>46235</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208186</t>
+          <t>207402</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>264264</t>
+          <t>263846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260030</t>
+          <t>258980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>311511</t>
+          <t>310331</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27638</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34873</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153220</t>
+          <t>152974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160863</t>
+          <t>160434</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>221740</t>
+          <t>221843</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>234346</t>
+          <t>234651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>377963</t>
+          <t>377998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>393156</t>
+          <t>393061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66947</t>
+          <t>66767</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97983</t>
+          <t>99445</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162248</t>
+          <t>162854</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120183</t>
+          <t>118878</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>245408</t>
+          <t>245815</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>391270</t>
+          <t>389808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>422306</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>734586</t>
+          <t>733980</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>838923</t>
+          <t>832125</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1140679</t>
+          <t>1140272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1265904</t>
+          <t>1267209</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140685</t>
+          <t>140592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306661</t>
+          <t>306744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342055</t>
+          <t>340286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353056</t>
+          <t>352427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>628255</t>
+          <t>628751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>639020</t>
+          <t>639011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218696</t>
+          <t>218508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>409637</t>
+          <t>409480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193223</t>
+          <t>192955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438456</t>
+          <t>438563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98303</t>
+          <t>98015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107239</t>
+          <t>107245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142364</t>
+          <t>141183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244121</t>
+          <t>244394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255692</t>
+          <t>255640</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171347</t>
+          <t>171104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>332577</t>
+          <t>332545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>346861</t>
+          <t>347393</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>437964</t>
+          <t>437933</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788911</t>
+          <t>788861</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>453296</t>
+          <t>454283</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>465078</t>
+          <t>465097</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>525847</t>
+          <t>526525</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>537073</t>
+          <t>537551</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>986557</t>
+          <t>987653</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1000665</t>
+          <t>1001223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,47 +3527,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>28781</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>18714</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>41885</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>28781</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>18664</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>41428</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1890151</t>
+          <t>1889452</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1904747</t>
+          <t>1904168</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2273189</t>
+          <t>2271553</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2291168</t>
+          <t>2290714</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4170160</t>
+          <t>4169703</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4192924</t>
+          <t>4192874</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168757</t>
+          <t>169012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176771</t>
+          <t>176744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189065</t>
+          <t>188718</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203990</t>
+          <t>203929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>361711</t>
+          <t>361423</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>379521</t>
+          <t>378946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312474</t>
+          <t>312041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350901</t>
+          <t>350458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>666121</t>
+          <t>666981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674281</t>
+          <t>674295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231262</t>
+          <t>229465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>436398</t>
+          <t>436234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>281524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290821</t>
+          <t>290808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525482</t>
+          <t>525685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>534558</t>
+          <t>534624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131174</t>
+          <t>134286</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300630</t>
+          <t>299466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169465</t>
+          <t>169261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>373545</t>
+          <t>374209</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21078</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>384067</t>
+          <t>383248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>395923</t>
+          <t>394979</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>442993</t>
+          <t>443196</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>453600</t>
+          <t>454419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>832471</t>
+          <t>832430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>848147</t>
+          <t>847445</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>469319</t>
+          <t>469358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>582216</t>
+          <t>582450</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1055456</t>
+          <t>1055465</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1064774</t>
+          <t>1064768</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61375</t>
+          <t>62658</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2108907</t>
+          <t>2109471</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2127599</t>
+          <t>2127848</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2475246</t>
+          <t>2473771</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2498774</t>
+          <t>2497186</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4592781</t>
+          <t>4591498</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4622464</t>
+          <t>4621482</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167757</t>
+          <t>167353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191573</t>
+          <t>193311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199318</t>
+          <t>199325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>364651</t>
+          <t>364336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372761</t>
+          <t>372683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>254862</t>
+          <t>254393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314948</t>
+          <t>314022</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>574138</t>
+          <t>571632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>583521</t>
+          <t>583456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172662</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206173</t>
+          <t>205959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>381979</t>
+          <t>382043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>388911</t>
+          <t>388902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>879</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247248</t>
+          <t>247334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>254775</t>
+          <t>254778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>439554</t>
+          <t>439521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>446302</t>
+          <t>446300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122648</t>
+          <t>122905</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132776</t>
+          <t>132166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268284</t>
+          <t>268225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278312</t>
+          <t>278308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153179</t>
+          <t>153206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160412</t>
+          <t>160413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165736</t>
+          <t>164804</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>323102</t>
+          <t>322978</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>331857</t>
+          <t>331980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>332562</t>
+          <t>333629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>435091</t>
+          <t>435166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>442544</t>
+          <t>442533</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>772347</t>
+          <t>772225</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>781788</t>
+          <t>781777</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>446724</t>
+          <t>447338</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>455695</t>
+          <t>455683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>567828</t>
+          <t>567237</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>580667</t>
+          <t>580028</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1020837</t>
+          <t>1018519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1035092</t>
+          <t>1034056</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54523</t>
+          <t>56166</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1869753</t>
+          <t>1868839</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1886093</t>
+          <t>1886447</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2301530</t>
+          <t>2301063</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2320099</t>
+          <t>2320272</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4177425</t>
+          <t>4175782</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4203913</t>
+          <t>4202784</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>13090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19948</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20316</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15583</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>27758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>36227</t>
+          <t>40991</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29851</t>
+          <t>35079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42323</t>
+          <t>46548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55837</t>
+          <t>60348</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55837</t>
+          <t>60348</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55837</t>
+          <t>60348</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>26730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>25701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33871</t>
+          <t>36066</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45066</t>
+          <t>48921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>53372</t>
+          <t>59663</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43649</t>
+          <t>50089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59825</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>94930</t>
+          <t>105781</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>98991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100905</t>
+          <t>111960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>148302</t>
+          <t>165445</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137107</t>
+          <t>152590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156259</t>
+          <t>175250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>112490</t>
+          <t>124692</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112490</t>
+          <t>124692</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112490</t>
+          <t>124692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>182173</t>
+          <t>201511</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>182173</t>
+          <t>201511</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>182173</t>
+          <t>201511</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>14726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>32923</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24208</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35024</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>39523</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>33842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44892</t>
+          <t>44934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>70103</t>
+          <t>71281</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61362</t>
+          <t>61674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77289</t>
+          <t>77980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>44544</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>44544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>44544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>59660</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>59660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>59660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>103433</t>
+          <t>104204</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103433</t>
+          <t>104204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103433</t>
+          <t>104204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41040</t>
+          <t>46307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>56346</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>44790</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51353</t>
+          <t>63799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61984</t>
+          <t>71629</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56258</t>
+          <t>66012</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66186</t>
+          <t>76461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>106854</t>
+          <t>127975</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95296</t>
+          <t>113363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114877</t>
+          <t>135985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60042</t>
+          <t>73103</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60042</t>
+          <t>73103</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60042</t>
+          <t>73103</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76294</t>
+          <t>86567</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76294</t>
+          <t>86567</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76294</t>
+          <t>86567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>136336</t>
+          <t>159670</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>136336</t>
+          <t>159670</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136336</t>
+          <t>159670</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18801</t>
+          <t>22716</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23641</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>49315</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>44577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45658</t>
+          <t>52918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>53417</t>
+          <t>60791</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53417</t>
+          <t>60791</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53417</t>
+          <t>60791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23264</t>
+          <t>24534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>30936</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24773</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38948</t>
+          <t>39021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>46532</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>40983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48707</t>
+          <t>51026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>54509</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47536</t>
+          <t>48093</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57090</t>
+          <t>58789</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>96916</t>
+          <t>101040</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88823</t>
+          <t>92955</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102998</t>
+          <t>107171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56971</t>
+          <t>59350</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56971</t>
+          <t>59350</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56971</t>
+          <t>59350</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>72627</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>72627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>72627</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>127771</t>
+          <t>131976</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>127771</t>
+          <t>131976</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127771</t>
+          <t>131976</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58498</t>
+          <t>24015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55304</t>
+          <t>32975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43373</t>
+          <t>51369</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38983</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>55116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>254320</t>
+          <t>65614</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>207402</t>
+          <t>57404</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>263846</t>
+          <t>71238</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>297693</t>
+          <t>116984</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258980</t>
+          <t>106292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>310331</t>
+          <t>124174</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48384</t>
+          <t>57847</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48384</t>
+          <t>57847</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48384</t>
+          <t>57847</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>265900</t>
+          <t>81419</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>265900</t>
+          <t>81419</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>265900</t>
+          <t>81419</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>314284</t>
+          <t>139267</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>314284</t>
+          <t>139267</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>314284</t>
+          <t>139267</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,22 +13133,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>33314</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34838</t>
+          <t>41704</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>157392</t>
+          <t>190413</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152974</t>
+          <t>184237</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160434</t>
+          <t>194088</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,27 +13246,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>228540</t>
+          <t>270670</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>221843</t>
+          <t>262028</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>234651</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>385934</t>
+          <t>461083</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>377998</t>
+          <t>451039</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>393061</t>
+          <t>469241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>163457</t>
+          <t>197402</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>163457</t>
+          <t>197402</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>163457</t>
+          <t>197402</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>249378</t>
+          <t>295342</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>249378</t>
+          <t>295342</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>249378</t>
+          <t>295342</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>412836</t>
+          <t>492743</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>412836</t>
+          <t>492743</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>412836</t>
+          <t>492743</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66767</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>99445</t>
+          <t>105299</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>64709</t>
+          <t>115664</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162854</t>
+          <t>147593</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>201617</t>
+          <t>216395</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>118878</t>
+          <t>194694</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>245815</t>
+          <t>241368</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>407919</t>
+          <t>475996</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>389808</t>
+          <t>455525</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>422486</t>
+          <t>490484</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>776551</t>
+          <t>658120</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>733980</t>
+          <t>642094</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>832125</t>
+          <t>674023</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1184470</t>
+          <t>1134116</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1140272</t>
+          <t>1109143</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1267209</t>
+          <t>1155817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
